--- a/diseases/d007/1995-1999.xlsx
+++ b/diseases/d007/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>65</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>13</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>40</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>19</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>25</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>5</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>18</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>8</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>22</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>20</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>32</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>27</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>29</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>43</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>17</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>48</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>13</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>38</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>20</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>42</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>21</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>61</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>6</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>41</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>10</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>51</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>24</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>47</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>32</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>37</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>30</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>38</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>30</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>24</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>25</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>51</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>53</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>37</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>48</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>36</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>17</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>30</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>14</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20406,9 +20259,6 @@
       <c r="O102" t="n">
         <v>53</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20799,9 +20649,6 @@
       <c r="O104" t="n">
         <v>21</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21337,9 +21184,6 @@
       <c r="O107" t="n">
         <v>53</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21730,9 +21574,6 @@
       <c r="O109" t="n">
         <v>15</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22268,9 +22109,6 @@
       <c r="O112" t="n">
         <v>46</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22661,9 +22499,6 @@
       <c r="O114" t="n">
         <v>18</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23199,9 +23034,6 @@
       <c r="O117" t="n">
         <v>35</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23592,9 +23424,6 @@
       <c r="O119" t="n">
         <v>29</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24130,9 +23959,6 @@
       <c r="O122" t="n">
         <v>16</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24523,9 +24349,6 @@
       <c r="O124" t="n">
         <v>54</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25061,9 +24884,6 @@
       <c r="O127" t="n">
         <v>17</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25454,9 +25274,6 @@
       <c r="O129" t="n">
         <v>44</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25992,9 +25809,6 @@
       <c r="O132" t="n">
         <v>12</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26385,9 +26199,6 @@
       <c r="O134" t="n">
         <v>27</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26923,9 +26734,6 @@
       <c r="O137" t="n">
         <v>15</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27316,9 +27124,6 @@
       <c r="O139" t="n">
         <v>19</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27854,9 +27659,6 @@
       <c r="O142" t="n">
         <v>26</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28247,9 +28049,6 @@
       <c r="O144" t="n">
         <v>28</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28785,9 +28584,6 @@
       <c r="O147" t="n">
         <v>33</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29178,9 +28974,6 @@
       <c r="O149" t="n">
         <v>19</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29716,9 +29509,6 @@
       <c r="O152" t="n">
         <v>30</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30109,9 +29899,6 @@
       <c r="O154" t="n">
         <v>12</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30647,9 +30434,6 @@
       <c r="O157" t="n">
         <v>21</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31040,9 +30824,6 @@
       <c r="O159" t="n">
         <v>6</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31817,9 +31598,6 @@
       <c r="O163" t="n">
         <v>26</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32210,9 +31988,6 @@
       <c r="O165" t="n">
         <v>3</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32748,9 +32523,6 @@
       <c r="O168" t="n">
         <v>32</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33141,9 +32913,6 @@
       <c r="O170" t="n">
         <v>9</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33679,9 +33448,6 @@
       <c r="O173" t="n">
         <v>35</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34072,9 +33838,6 @@
       <c r="O175" t="n">
         <v>12</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34610,9 +34373,6 @@
       <c r="O178" t="n">
         <v>27</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35003,9 +34763,6 @@
       <c r="O180" t="n">
         <v>6</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35541,9 +35298,6 @@
       <c r="O183" t="n">
         <v>11</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="S183" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35934,9 +35688,6 @@
       <c r="O185" t="n">
         <v>8</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36472,9 +36223,6 @@
       <c r="O188" t="n">
         <v>14</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36865,9 +36613,6 @@
       <c r="O190" t="n">
         <v>8</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37403,9 +37148,6 @@
       <c r="O193" t="n">
         <v>17</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37796,9 +37538,6 @@
       <c r="O195" t="n">
         <v>16</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38334,9 +38073,6 @@
       <c r="O198" t="n">
         <v>19</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38727,9 +38463,6 @@
       <c r="O200" t="n">
         <v>18</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39265,9 +38998,6 @@
       <c r="O203" t="n">
         <v>27</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39658,9 +39388,6 @@
       <c r="O205" t="n">
         <v>9</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40196,9 +39923,6 @@
       <c r="O208" t="n">
         <v>60</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40589,9 +40313,6 @@
       <c r="O210" t="n">
         <v>17</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41127,9 +40848,6 @@
       <c r="O213" t="n">
         <v>59</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41520,9 +41238,6 @@
       <c r="O215" t="n">
         <v>7</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42058,9 +41773,6 @@
       <c r="O218" t="n">
         <v>102</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42451,9 +42163,6 @@
       <c r="O220" t="n">
         <v>5</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43228,9 +42937,6 @@
       <c r="O224" t="n">
         <v>189</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43621,9 +43327,6 @@
       <c r="O226" t="n">
         <v>4</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44159,9 +43862,6 @@
       <c r="O229" t="n">
         <v>187</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44552,9 +44252,6 @@
       <c r="O231" t="n">
         <v>3</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45090,9 +44787,6 @@
       <c r="O234" t="n">
         <v>133</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45483,9 +45177,6 @@
       <c r="O236" t="n">
         <v>2</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46021,9 +45712,6 @@
       <c r="O239" t="n">
         <v>127</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46414,9 +46102,6 @@
       <c r="O241" t="n">
         <v>3</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46952,9 +46637,6 @@
       <c r="O244" t="n">
         <v>74</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47345,9 +47027,6 @@
       <c r="O246" t="n">
         <v>1</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47883,9 +47562,6 @@
       <c r="O249" t="n">
         <v>72</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48276,9 +47952,6 @@
       <c r="O251" t="n">
         <v>3</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48814,9 +48487,6 @@
       <c r="O254" t="n">
         <v>66</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49207,9 +48877,6 @@
       <c r="O256" t="n">
         <v>6</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49745,9 +49412,6 @@
       <c r="O259" t="n">
         <v>58</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50138,9 +49802,6 @@
       <c r="O261" t="n">
         <v>7</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50676,9 +50337,6 @@
       <c r="O264" t="n">
         <v>62</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51069,9 +50727,6 @@
       <c r="O266" t="n">
         <v>2</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51607,9 +51262,6 @@
       <c r="O269" t="n">
         <v>33</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52000,9 +51652,6 @@
       <c r="O271" t="n">
         <v>3</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52538,9 +52187,6 @@
       <c r="O274" t="n">
         <v>31</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="S274" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52931,9 +52577,6 @@
       <c r="O276" t="n">
         <v>9</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53468,9 +53111,6 @@
       </c>
       <c r="O279" t="n">
         <v>17</v>
-      </c>
-      <c r="Q279" t="n">
-        <v>0</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
